--- a/data/availability/projects/palm-hills-developments/the-crown-extension.xlsx
+++ b/data/availability/projects/palm-hills-developments/the-crown-extension.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for the-crown-extension</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -759,7 +769,6 @@
       <c r="G2" t="n">
         <v>217</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -816,7 +825,6 @@
       <c r="G3" t="n">
         <v>217</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -873,7 +881,6 @@
       <c r="G4" t="n">
         <v>223</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -930,7 +937,6 @@
       <c r="G5" t="n">
         <v>217</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -987,7 +993,6 @@
       <c r="G6" t="n">
         <v>217</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1044,7 +1049,6 @@
       <c r="G7" t="n">
         <v>223</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1101,7 +1105,6 @@
       <c r="G8" t="n">
         <v>223</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1158,7 +1161,6 @@
       <c r="G9" t="n">
         <v>217</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1215,7 +1217,6 @@
       <c r="G10" t="n">
         <v>223</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1272,7 +1273,6 @@
       <c r="G11" t="n">
         <v>217</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1329,7 +1329,6 @@
       <c r="G12" t="n">
         <v>217</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1386,7 +1385,6 @@
       <c r="G13" t="n">
         <v>223</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1443,7 +1441,6 @@
       <c r="G14" t="n">
         <v>223</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1500,7 +1497,6 @@
       <c r="G15" t="n">
         <v>217</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1557,7 +1553,6 @@
       <c r="G16" t="n">
         <v>217</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1614,7 +1609,6 @@
       <c r="G17" t="n">
         <v>223</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1671,7 +1665,6 @@
       <c r="G18" t="n">
         <v>223</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1728,7 +1721,6 @@
       <c r="G19" t="n">
         <v>217</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1785,7 +1777,6 @@
       <c r="G20" t="n">
         <v>217</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1842,7 +1833,6 @@
       <c r="G21" t="n">
         <v>223</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1899,7 +1889,6 @@
       <c r="G22" t="n">
         <v>223</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1956,7 +1945,6 @@
       <c r="G23" t="n">
         <v>217</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2013,7 +2001,6 @@
       <c r="G24" t="n">
         <v>217</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2070,7 +2057,6 @@
       <c r="G25" t="n">
         <v>223</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2127,7 +2113,6 @@
       <c r="G26" t="n">
         <v>223</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2184,7 +2169,6 @@
       <c r="G27" t="n">
         <v>217</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2241,7 +2225,6 @@
       <c r="G28" t="n">
         <v>223</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2298,7 +2281,6 @@
       <c r="G29" t="n">
         <v>217</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2355,7 +2337,6 @@
       <c r="G30" t="n">
         <v>223</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2412,7 +2393,6 @@
       <c r="G31" t="n">
         <v>217</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2469,7 +2449,6 @@
       <c r="G32" t="n">
         <v>217</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2526,7 +2505,6 @@
       <c r="G33" t="n">
         <v>223</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2583,7 +2561,6 @@
       <c r="G34" t="n">
         <v>223</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2640,7 +2617,6 @@
       <c r="G35" t="n">
         <v>217</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2697,7 +2673,6 @@
       <c r="G36" t="n">
         <v>217</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2754,7 +2729,6 @@
       <c r="G37" t="n">
         <v>223</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2811,7 +2785,6 @@
       <c r="G38" t="n">
         <v>223</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2868,7 +2841,6 @@
       <c r="G39" t="n">
         <v>217</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2925,7 +2897,6 @@
       <c r="G40" t="n">
         <v>217</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2982,7 +2953,6 @@
       <c r="G41" t="n">
         <v>223</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3039,7 +3009,6 @@
       <c r="G42" t="n">
         <v>223</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3096,7 +3065,6 @@
       <c r="G43" t="n">
         <v>217</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3153,7 +3121,6 @@
       <c r="G44" t="n">
         <v>217</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3210,7 +3177,6 @@
       <c r="G45" t="n">
         <v>223</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3267,7 +3233,6 @@
       <c r="G46" t="n">
         <v>223</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3324,7 +3289,6 @@
       <c r="G47" t="n">
         <v>217</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3381,7 +3345,6 @@
       <c r="G48" t="n">
         <v>217</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3438,7 +3401,6 @@
       <c r="G49" t="n">
         <v>223</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3495,7 +3457,6 @@
       <c r="G50" t="n">
         <v>223</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3552,7 +3513,6 @@
       <c r="G51" t="n">
         <v>217</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3609,7 +3569,6 @@
       <c r="G52" t="n">
         <v>225.5</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3666,7 +3625,6 @@
       <c r="G53" t="n">
         <v>225.5</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3723,7 +3681,6 @@
       <c r="G54" t="n">
         <v>225.5</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/the-crown-extension.xlsx
+++ b/data/availability/projects/palm-hills-developments/the-crown-extension.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
